--- a/data/cepea-consulta-robusta.reparado.xlsx
+++ b/data/cepea-consulta-robusta.reparado.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\painel-controle-commodities\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C11089B9-039A-4DAA-98A6-CDA3A9459C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9B43A45-FD8F-45AF-A6D8-411C7B7FEDAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
   </bookViews>

--- a/data/cepea-consulta-robusta.reparado.xlsx
+++ b/data/cepea-consulta-robusta.reparado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9B43A45-FD8F-45AF-A6D8-411C7B7FEDAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B14B403A-0B76-4E74-B3C1-14E4C418BDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
+    <workbookView xWindow="3240" yWindow="2052" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Plan 1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="1212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="1233">
   <si>
     <t>Café | INDICADOR DO CAFÉ ROBUSTA CEPEA/ESALQ</t>
   </si>
@@ -3668,6 +3668,69 @@
   </si>
   <si>
     <t>215,27</t>
+  </si>
+  <si>
+    <t>14/08/2025</t>
+  </si>
+  <si>
+    <t>1.179,05</t>
+  </si>
+  <si>
+    <t>217,66</t>
+  </si>
+  <si>
+    <t>15/08/2025</t>
+  </si>
+  <si>
+    <t>1.231,19</t>
+  </si>
+  <si>
+    <t>228,08</t>
+  </si>
+  <si>
+    <t>18/08/2025</t>
+  </si>
+  <si>
+    <t>1.231,40</t>
+  </si>
+  <si>
+    <t>226,65</t>
+  </si>
+  <si>
+    <t>19/08/2025</t>
+  </si>
+  <si>
+    <t>1.299,95</t>
+  </si>
+  <si>
+    <t>236,31</t>
+  </si>
+  <si>
+    <t>20/08/2025</t>
+  </si>
+  <si>
+    <t>1.383,84</t>
+  </si>
+  <si>
+    <t>252,85</t>
+  </si>
+  <si>
+    <t>21/08/2025</t>
+  </si>
+  <si>
+    <t>1.424,45</t>
+  </si>
+  <si>
+    <t>259,94</t>
+  </si>
+  <si>
+    <t>22/08/2025</t>
+  </si>
+  <si>
+    <t>1.452,77</t>
+  </si>
+  <si>
+    <t>267,79</t>
   </si>
 </sst>
 </file>
@@ -4119,7 +4182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J409"/>
+  <dimension ref="A1:J416"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
@@ -8637,6 +8700,83 @@
       </c>
       <c r="C409" s="3" t="s">
         <v>1211</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A410" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B410" s="3" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C410" s="3" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A411" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B411" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C411" s="3" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A412" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B412" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C412" s="3" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A413" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B413" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C413" s="3" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A414" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B414" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C414" s="3" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A415" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B415" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C415" s="3" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A416" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B416" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C416" s="3" t="s">
+        <v>1232</v>
       </c>
     </row>
   </sheetData>

--- a/data/cepea-consulta-robusta.reparado.xlsx
+++ b/data/cepea-consulta-robusta.reparado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B14B403A-0B76-4E74-B3C1-14E4C418BDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6957714D-13B6-473D-A3D7-C6E582E4DD81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3240" yWindow="2052" windowWidth="17280" windowHeight="8964"/>
   </bookViews>

--- a/data/cepea-consulta-robusta.reparado.xlsx
+++ b/data/cepea-consulta-robusta.reparado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6957714D-13B6-473D-A3D7-C6E582E4DD81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9E9AC94-5154-4401-A964-30461F4A21E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="2052" windowWidth="17280" windowHeight="8964"/>
+    <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Plan 1" sheetId="1" r:id="rId1"/>

--- a/data/cepea-consulta-robusta.reparado.xlsx
+++ b/data/cepea-consulta-robusta.reparado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9E9AC94-5154-4401-A964-30461F4A21E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B89E93F8-78E1-4F87-B1B2-FF8802936B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="1233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="1245">
   <si>
     <t>Café | INDICADOR DO CAFÉ ROBUSTA CEPEA/ESALQ</t>
   </si>
@@ -3731,6 +3731,42 @@
   </si>
   <si>
     <t>267,79</t>
+  </si>
+  <si>
+    <t>25/08/2025</t>
+  </si>
+  <si>
+    <t>1.469,43</t>
+  </si>
+  <si>
+    <t>271,36</t>
+  </si>
+  <si>
+    <t>26/08/2025</t>
+  </si>
+  <si>
+    <t>1.510,92</t>
+  </si>
+  <si>
+    <t>278,00</t>
+  </si>
+  <si>
+    <t>27/08/2025</t>
+  </si>
+  <si>
+    <t>1.548,95</t>
+  </si>
+  <si>
+    <t>285,73</t>
+  </si>
+  <si>
+    <t>28/08/2025</t>
+  </si>
+  <si>
+    <t>1.529,97</t>
+  </si>
+  <si>
+    <t>283,06</t>
   </si>
 </sst>
 </file>
@@ -4182,7 +4218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J416"/>
+  <dimension ref="A1:J420"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
@@ -8777,6 +8813,50 @@
       </c>
       <c r="C416" s="3" t="s">
         <v>1232</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A417" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B417" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C417" s="3" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A418" s="3" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B418" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C418" s="3" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A419" s="3" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B419" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C419" s="3" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A420" s="3" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B420" s="3" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C420" s="3" t="s">
+        <v>1244</v>
       </c>
     </row>
   </sheetData>
